--- a/artfynd/A 6176-2022 artfynd.xlsx
+++ b/artfynd/A 6176-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6176-2022 artfynd.xlsx
+++ b/artfynd/A 6176-2022 artfynd.xlsx
@@ -2066,11 +2066,11 @@
         <v>56002723</v>
       </c>
       <c r="B13" t="n">
-        <v>95597</v>
+        <v>97278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567245.3391152672</v>
+        <v>567245</v>
       </c>
       <c r="R13" t="n">
-        <v>6943068.506015269</v>
+        <v>6943069</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2156,19 +2156,9 @@
           <t>2015-09-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2015-09-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 6176-2022 artfynd.xlsx
+++ b/artfynd/A 6176-2022 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>56002723</v>
       </c>
       <c r="B13" t="n">
-        <v>97278</v>
+        <v>97279</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2144,11 +2144,6 @@
       <c r="W13" t="inlineStr">
         <is>
           <t>Torp</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Y-Ång-0077</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">

--- a/artfynd/A 6176-2022 artfynd.xlsx
+++ b/artfynd/A 6176-2022 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>56002723</v>
       </c>
       <c r="B13" t="n">
-        <v>97279</v>
+        <v>97282</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 6176-2022 artfynd.xlsx
+++ b/artfynd/A 6176-2022 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>56002723</v>
       </c>
       <c r="B13" t="n">
-        <v>97385</v>
+        <v>97393</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 6176-2022 artfynd.xlsx
+++ b/artfynd/A 6176-2022 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>56002723</v>
       </c>
       <c r="B13" t="n">
-        <v>97393</v>
+        <v>97395</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 6176-2022 artfynd.xlsx
+++ b/artfynd/A 6176-2022 artfynd.xlsx
@@ -2066,7 +2066,7 @@
         <v>56002723</v>
       </c>
       <c r="B13" t="n">
-        <v>97395</v>
+        <v>97403</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
